--- a/reservation_forms/006_catering_request_form_milk_honey--reservation_forms.xlsx
+++ b/reservation_forms/006_catering_request_form_milk_honey--reservation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mediterranean</t>
+          <t>asian_fusion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mediterranean</t>
+          <t>Asian Fusion</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>asian_fusion</t>
+          <t>farm-to-table</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Asian Fusion</t>
+          <t>Farm-to-Table</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>farm-to-table</t>
+          <t>gourmet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Farm-to-Table</t>
+          <t>Gourmet</t>
         </is>
       </c>
     </row>
@@ -1648,29 +1648,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gourmet</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gourmet</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cuisine_type_choices</t>
+          <t>additional_services_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>linens_and_place_settings</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Linens and Place Settings</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>linens_and_place_settings</t>
+          <t>floral_arrangements</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Linens and Place Settings</t>
+          <t>Floral Arrangements</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>floral_arrangements</t>
+          <t>cake_cutting_service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Floral Arrangements</t>
+          <t>Cake Cutting Service</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cake_cutting_service</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cake Cutting Service</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>photography</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>setup_and_cleanup</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Setup and Cleanup</t>
         </is>
       </c>
     </row>
@@ -1767,27 +1767,10 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>setup_and_cleanup</t>
+          <t>equipment_rental</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
-        <is>
-          <t>Setup and Cleanup</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>additional_services_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>equipment_rental</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>Equipment Rental</t>
         </is>
